--- a/data/trans_camb/P57GLOBAL_R-Estudios-trans_camb.xlsx
+++ b/data/trans_camb/P57GLOBAL_R-Estudios-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-7,16; 0,77</t>
+          <t>-7,5; 0,78</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1,65; 9,8</t>
+          <t>2,06; 9,95</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-13,55; -3,94</t>
+          <t>-13,89; -4,01</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-4,84; 1,25</t>
+          <t>-4,86; 1,48</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>5,45; 11,64</t>
+          <t>5,75; 11,59</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-11,26; -4,5</t>
+          <t>-11,21; -4,41</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-4,66; 0,32</t>
+          <t>-4,59; 0,54</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>5,16; 9,78</t>
+          <t>5,02; 9,99</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-11,01; -5,4</t>
+          <t>-10,95; -5,42</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-9,07; 1,07</t>
+          <t>-9,47; 1,11</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>2,17; 13,2</t>
+          <t>2,74; 13,55</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-17,71; -5,39</t>
+          <t>-17,95; -5,33</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-6,0; 1,63</t>
+          <t>-6,04; 1,94</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>6,75; 14,98</t>
+          <t>7,12; 14,95</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-14,0; -5,79</t>
+          <t>-13,92; -5,74</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-5,89; 0,43</t>
+          <t>-5,83; 0,71</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>6,48; 12,73</t>
+          <t>6,36; 13,11</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-13,96; -7,02</t>
+          <t>-13,88; -7,12</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-3,69; 2,39</t>
+          <t>-4,17; 2,38</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>12,47; 18,22</t>
+          <t>12,57; 18,66</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-31,98; -4,17</t>
+          <t>-29,43; -4,09</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>3,71; 10,15</t>
+          <t>3,73; 10,13</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>14,41; 19,72</t>
+          <t>14,09; 20,22</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-15,32; -3,52</t>
+          <t>-14,05; -3,33</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,86; 5,21</t>
+          <t>0,74; 5,28</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>14,2; 18,5</t>
+          <t>14,23; 18,19</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-22,27; -5,2</t>
+          <t>-22,88; -5,11</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-5,29; 3,67</t>
+          <t>-6,02; 3,58</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>17,78; 27,56</t>
+          <t>18,2; 28,39</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-46,71; -6,3</t>
+          <t>-43,41; -6,02</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>5,3; 15,12</t>
+          <t>5,3; 15,0</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>20,34; 29,42</t>
+          <t>19,92; 30,07</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-22,18; -5,23</t>
+          <t>-20,16; -4,99</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>1,28; 7,82</t>
+          <t>1,07; 7,94</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>20,23; 27,6</t>
+          <t>20,4; 27,22</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-32,21; -7,75</t>
+          <t>-33,38; -7,66</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-7,19; 5,2</t>
+          <t>-7,2; 5,31</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>2,73; 13,78</t>
+          <t>2,11; 13,55</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-13,33; -1,51</t>
+          <t>-13,6; -1,58</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-3,89; 9,59</t>
+          <t>-3,16; 8,95</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>5,4; 17,12</t>
+          <t>5,19; 16,65</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-13,1; -2,35</t>
+          <t>-13,22; -1,98</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-3,74; 4,91</t>
+          <t>-3,64; 5,09</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>5,87; 13,76</t>
+          <t>5,25; 13,17</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-11,96; -3,81</t>
+          <t>-11,99; -3,83</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-10,09; 7,82</t>
+          <t>-9,95; 8,1</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>3,85; 20,95</t>
+          <t>3,08; 20,6</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-18,45; -2,32</t>
+          <t>-19,3; -2,47</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-5,71; 16,05</t>
+          <t>-4,72; 14,59</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>7,91; 27,95</t>
+          <t>7,62; 27,22</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-19,27; -3,73</t>
+          <t>-19,62; -3,43</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-5,52; 7,54</t>
+          <t>-5,28; 7,86</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>8,64; 21,52</t>
+          <t>7,51; 20,41</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-17,28; -5,91</t>
+          <t>-17,37; -5,91</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-3,95; 0,83</t>
+          <t>-4,02; 0,53</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>9,44; 13,78</t>
+          <t>9,28; 13,51</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-26,51; -6,45</t>
+          <t>-27,29; -6,74</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,65; 5,06</t>
+          <t>0,7; 5,03</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>10,6; 14,5</t>
+          <t>10,35; 14,47</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-14,4; -7,33</t>
+          <t>-14,82; -7,22</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-0,93; 2,26</t>
+          <t>-0,7; 2,36</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>10,57; 13,41</t>
+          <t>10,47; 13,36</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-19,81; -7,96</t>
+          <t>-18,05; -7,77</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-5,5; 1,19</t>
+          <t>-5,62; 0,8</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>13,21; 20,1</t>
+          <t>12,94; 19,53</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-38,26; -9,29</t>
+          <t>-38,88; -9,57</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>0,89; 7,14</t>
+          <t>0,94; 7,07</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>14,5; 20,42</t>
+          <t>14,11; 20,39</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-19,87; -10,24</t>
+          <t>-20,36; -10,02</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-1,27; 3,2</t>
+          <t>-0,97; 3,34</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>14,67; 18,94</t>
+          <t>14,49; 18,93</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-27,52; -11,16</t>
+          <t>-25,21; -10,89</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P57GLOBAL_R-Estudios-trans_camb.xlsx
+++ b/data/trans_camb/P57GLOBAL_R-Estudios-trans_camb.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>-8,72</t>
+          <t>-8,25</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>-7,91</t>
+          <t>-6,9</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>-8,14</t>
+          <t>-7,38</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-7,5; 0,78</t>
+          <t>-7,08; 0,93</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>2,06; 9,95</t>
+          <t>2,42; 9,82</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-13,89; -4,01</t>
+          <t>-13,15; -3,55</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-4,86; 1,48</t>
+          <t>-5,17; 1,57</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>5,75; 11,59</t>
+          <t>5,74; 11,75</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-11,21; -4,41</t>
+          <t>-10,1; -3,72</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-4,59; 0,54</t>
+          <t>-4,8; 0,17</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>5,02; 9,99</t>
+          <t>5,21; 9,91</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-10,95; -5,42</t>
+          <t>-10,12; -4,63</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>-11,51%</t>
+          <t>-10,88%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>-9,99%</t>
+          <t>-8,72%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>-10,47%</t>
+          <t>-9,5%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-9,47; 1,11</t>
+          <t>-9,2; 1,23</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>2,74; 13,55</t>
+          <t>3,07; 13,36</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-17,95; -5,33</t>
+          <t>-16,95; -4,82</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-6,04; 1,94</t>
+          <t>-6,43; 2,02</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>7,12; 14,95</t>
+          <t>7,02; 15,26</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-13,92; -5,74</t>
+          <t>-12,46; -4,73</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-5,83; 0,71</t>
+          <t>-6,03; 0,22</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>6,36; 13,11</t>
+          <t>6,66; 12,95</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-13,88; -7,12</t>
+          <t>-12,81; -6,06</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>-11,84</t>
+          <t>-3,55</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>-7,62</t>
+          <t>-3,53</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>-9,88</t>
+          <t>-3,53</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-4,17; 2,38</t>
+          <t>-3,84; 2,65</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>12,57; 18,66</t>
+          <t>12,54; 18,24</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-29,43; -4,09</t>
+          <t>-6,96; -0,29</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>3,73; 10,13</t>
+          <t>3,48; 9,84</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>14,09; 20,22</t>
+          <t>13,73; 19,47</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-14,05; -3,33</t>
+          <t>-6,19; -0,41</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,74; 5,28</t>
+          <t>0,63; 5,2</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>14,23; 18,19</t>
+          <t>14,06; 18,06</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-22,88; -5,11</t>
+          <t>-5,75; -1,28</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>-17,47%</t>
+          <t>-5,23%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>-11,06%</t>
+          <t>-5,12%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>-14,46%</t>
+          <t>-5,17%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-6,02; 3,58</t>
+          <t>-5,52; 4,03</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>18,2; 28,39</t>
+          <t>18,07; 27,67</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-43,41; -6,02</t>
+          <t>-10,07; -0,45</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>5,3; 15,0</t>
+          <t>4,92; 14,67</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>19,92; 30,07</t>
+          <t>19,34; 29,13</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-20,16; -4,99</t>
+          <t>-8,82; -0,61</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>1,07; 7,94</t>
+          <t>0,89; 7,75</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>20,4; 27,22</t>
+          <t>20,19; 27,01</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-33,38; -7,66</t>
+          <t>-8,18; -1,91</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>-7,6</t>
+          <t>-6,67</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>-7,88</t>
+          <t>-6,99</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>-7,91</t>
+          <t>-7,01</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-7,2; 5,31</t>
+          <t>-7,35; 5,06</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>2,11; 13,55</t>
+          <t>2,07; 13,9</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-13,6; -1,58</t>
+          <t>-12,83; -1,39</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-3,16; 8,95</t>
+          <t>-3,84; 8,82</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>5,19; 16,65</t>
+          <t>5,47; 17,01</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-13,22; -1,98</t>
+          <t>-12,58; -1,69</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-3,64; 5,09</t>
+          <t>-3,67; 5,45</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>5,25; 13,17</t>
+          <t>5,31; 13,34</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-11,99; -3,83</t>
+          <t>-11,04; -3,34</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>-11,08%</t>
+          <t>-9,73%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>-12,19%</t>
+          <t>-10,81%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>-11,85%</t>
+          <t>-10,5%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-9,95; 8,1</t>
+          <t>-10,38; 7,65</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>3,08; 20,6</t>
+          <t>2,88; 21,45</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-19,3; -2,47</t>
+          <t>-17,92; -2,11</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-4,72; 14,59</t>
+          <t>-5,81; 14,11</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>7,62; 27,22</t>
+          <t>7,76; 27,61</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-19,62; -3,43</t>
+          <t>-18,34; -2,57</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-5,28; 7,86</t>
+          <t>-5,36; 8,46</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>7,51; 20,41</t>
+          <t>7,61; 20,36</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-17,37; -5,91</t>
+          <t>-15,93; -5,05</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>-11,93</t>
+          <t>-6,14</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>-9,75</t>
+          <t>-6,97</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>-10,86</t>
+          <t>-6,56</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-4,02; 0,53</t>
+          <t>-3,88; 0,65</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>9,28; 13,51</t>
+          <t>9,4; 13,5</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-27,29; -6,74</t>
+          <t>-8,46; -3,73</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,7; 5,03</t>
+          <t>1,12; 5,2</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>10,35; 14,47</t>
+          <t>10,71; 14,45</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-14,82; -7,22</t>
+          <t>-9,35; -4,77</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-0,7; 2,36</t>
+          <t>-0,59; 2,3</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>10,47; 13,36</t>
+          <t>10,55; 13,41</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-18,05; -7,77</t>
+          <t>-8,28; -4,87</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>-16,93%</t>
+          <t>-8,72%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>-13,49%</t>
+          <t>-9,64%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>-15,21%</t>
+          <t>-9,19%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-5,62; 0,8</t>
+          <t>-5,41; 0,95</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>12,94; 19,53</t>
+          <t>13,22; 19,59</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-38,88; -9,57</t>
+          <t>-11,88; -5,39</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>0,94; 7,07</t>
+          <t>1,53; 7,32</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>14,11; 20,39</t>
+          <t>14,62; 20,43</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-20,36; -10,02</t>
+          <t>-12,68; -6,69</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-0,97; 3,34</t>
+          <t>-0,82; 3,24</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>14,49; 18,93</t>
+          <t>14,66; 19,08</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-25,21; -10,89</t>
+          <t>-11,48; -6,9</t>
         </is>
       </c>
     </row>
